--- a/data/sample/payroll.xlsx
+++ b/data/sample/payroll.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>E1024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>E1025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>E1026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
